--- a/feedback_surveys/032_satisfaction_survey_for_eco_friendly_products--feedback_surveys.xlsx
+++ b/feedback_surveys/032_satisfaction_survey_for_eco_friendly_products--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1213,12 +1213,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1263,29 +1263,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'likely'}</t>
+          <t>product_quality</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Likely'}</t>
+          <t>Product quality</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'product_quality'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Product quality'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'price'}</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Price'}</t>
+          <t>Availability</t>
         </is>
       </c>
     </row>
@@ -1331,29 +1331,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'availability'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Availability'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1382,29 +1382,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question7_choices</t>
+          <t>question11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1416,29 +1416,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question11_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1450,29 +1450,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question12_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'quality'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Quality'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'price'}</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Price'}</t>
+          <t>Availability</t>
         </is>
       </c>
     </row>
@@ -1518,29 +1518,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'availability'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Availability'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question13_choices</t>
+          <t>question14_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1552,29 +1552,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question14_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1620,29 +1620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>less_than_monthly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Less than monthly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question16_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_monthly'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Less than monthly'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1654,29 +1654,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question19_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1688,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question20_choices</t>
+          <t>question24_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1722,29 +1722,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question24_choices</t>
+          <t>question25_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1756,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question25_choices</t>
+          <t>question26_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1790,29 +1790,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question26_choices</t>
+          <t>question30_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1824,29 +1824,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question30_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
